--- a/LLM_Hosting_Cost_Calculator.xlsx
+++ b/LLM_Hosting_Cost_Calculator.xlsx
@@ -472,7 +472,7 @@
     <t xml:space="preserve">Engineer hours per month</t>
   </si>
   <si>
-    <t xml:space="preserve">Comes from the table on the Rates tab: Low 20, Medium 60, High 160 hours.</t>
+    <t xml:space="preserve">Comes from the table on the Rates tab: Low 10, Medium 20, High 30 hours.</t>
   </si>
   <si>
     <t xml:space="preserve">Override the hours (optional)</t>
@@ -1687,19 +1687,19 @@
     <t xml:space="preserve">Small models - up to 13 billion parameters</t>
   </si>
   <si>
-    <t xml:space="preserve">Keeping the lights on: patching, monitoring alerts, occasional restarts. Roughly half a day a week.</t>
+    <t xml:space="preserve">Keeping the lights on: patching, monitoring alerts, occasional restarts. A couple of hours a week.</t>
   </si>
   <si>
     <t xml:space="preserve">Medium models - 14 to 70 billion parameters</t>
   </si>
   <si>
-    <t xml:space="preserve">The above plus tuning, capacity changes, incident response and version upgrades. Roughly one and a half days a week.</t>
+    <t xml:space="preserve">The above plus tuning, capacity changes, incident response and version upgrades. About half a day a week.</t>
   </si>
   <si>
     <t xml:space="preserve">Large models - more than 70 billion parameters</t>
   </si>
   <si>
-    <t xml:space="preserve">A dedicated engineer: multi-GPU orchestration, performance work, on-call cover, cost control. About one full-time person.</t>
+    <t xml:space="preserve">Multi-GPU orchestration, performance work, on-call cover, cost control. Under a day a week.</t>
   </si>
   <si>
     <t xml:space="preserve">Set on the Calculator tab, step 5. Shown here for reference only.</t>
@@ -2041,13 +2041,13 @@
     <t xml:space="preserve">Support and labour (step 5)</t>
   </si>
   <si>
-    <t xml:space="preserve">The machines are only part of the cost - somebody has to run them. Step 5 recommends a support level from your model size: Low for models up to 13 billion parameters, Medium up to 70 billion, High above that. Low is about 20 engineer hours a month, Medium 60, and High 160, which is roughly one full-time person. At $116 an hour that is $2,320, $6,960 or $18,560 a month.</t>
+    <t xml:space="preserve">The machines are only part of the cost - somebody has to run them. Step 5 recommends a support level from your model size: Low for models up to 13 billion parameters, Medium up to 70 billion, High above that. Low is 10 engineer hours a month, Medium 20, and High 30. At $116 an hour that is $1,160, $2,320 or $3,480 a month.</t>
   </si>
   <si>
     <t xml:space="preserve">You can override all of it. Change the support level in the drop-down, type your own number of hours in the override box, or change the hourly rate. The hours table and the size thresholds live on the Rates tab if you want to reset the defaults for your organisation.</t>
   </si>
   <si>
-    <t xml:space="preserve">For smaller models this is often the largest single line on the bill - larger than the GPUs. That is normal and worth showing your finance team.</t>
+    <t xml:space="preserve">For small models the support line can still rival the GPU bill itself. That is normal and worth showing your finance team - and a good argument for one engineer supporting several models.</t>
   </si>
   <si>
     <t xml:space="preserve">The tabs</t>
@@ -2257,7 +2257,7 @@
     <t xml:space="preserve">Applied to every support level. Editable on the Calculator tab, step 5.</t>
   </si>
   <si>
-    <t xml:space="preserve">Support hours per level (Low 20, Medium 60, High 160) and the 13B / 70B size thresholds</t>
+    <t xml:space="preserve">Support hours per level (Low 10, Medium 20, High 30) and the 13B / 70B size thresholds</t>
   </si>
   <si>
     <t xml:space="preserve">Planning assumption, not a published figure</t>
@@ -2266,7 +2266,7 @@
     <t xml:space="preserve">-</t>
   </si>
   <si>
-    <t xml:space="preserve">High is about one full-time engineer. Adjust all five numbers in section H of the Rates tab to match how your team actually works.</t>
+    <t xml:space="preserve">Lightweight support assumption - under a day a week even at High. Adjust all five numbers in section H of the Rates tab to match how your team actually works.</t>
   </si>
   <si>
     <t xml:space="preserve">Gemini model pricing on Vertex AI / Agent Platform</t>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="C20" s="12" t="n">
         <f aca="false">IFERROR(B20/$B$25,0)</f>
-        <v>0.415597684586576</v>
+        <v>0.668606656437706</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="C21" s="12" t="n">
         <f aca="false">IFERROR(B21/$B$25,0)</f>
-        <v>0.00330295204642101</v>
+        <v>0.00531373442642842</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3744,7 +3744,7 @@
       </c>
       <c r="C22" s="12" t="n">
         <f aca="false">IFERROR(B22/$B$25,0)</f>
-        <v>0.0134809376116887</v>
+        <v>0.0216879086589782</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3766,11 +3766,11 @@
       </c>
       <c r="B24" s="11" t="n">
         <f aca="false">Calculator!$B$52</f>
-        <v>6960</v>
+        <v>2320</v>
       </c>
       <c r="C24" s="12" t="n">
         <f aca="false">IFERROR(B24/$B$25,0)</f>
-        <v>0.567618425755314</v>
+        <v>0.304391700476887</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="B25" s="14" t="n">
         <f aca="false">Calculator!$B$53</f>
-        <v>12261.7584</v>
+        <v>7621.7584</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="B26" s="16" t="n">
         <f aca="false">Calculator!$B$54</f>
-        <v>147141.1008</v>
+        <v>91461.1008</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="C29" s="17" t="n">
         <f aca="false">Comparison!$B$22</f>
-        <v>13083.169264</v>
+        <v>8443.169264</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="C30" s="17" t="n">
         <f aca="false">Comparison!$C$22</f>
-        <v>12261.7584</v>
+        <v>7621.7584</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="B31" s="19" t="str">
         <f aca="false">Comparison!$B$25</f>
-        <v>Microsoft Azure saves about $821 per month (6.3% less)</v>
+        <v>Microsoft Azure saves about $821 per month (9.7% less)</v>
       </c>
       <c r="C31" s="19"/>
       <c r="D31" s="19"/>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="B38" s="20" t="str">
         <f aca="false">IF(Inference!$B$6=Rates!$I$46,"n/a - traffic not specified",TEXT(Inference!$B$31,"$#,##0.00"))</f>
-        <v>$61.31</v>
+        <v>$38.11</v>
       </c>
       <c r="C38" s="10" t="s">
         <v>35</v>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="B39" s="7" t="str">
         <f aca="false">IF(Inference!$B$6=Rates!$I$46,"n/a",TEXT(Inference!$B$32,"$#,##0.00"))</f>
-        <v>$24.52</v>
+        <v>$15.24</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="B41" s="21" t="str">
         <f aca="false">IF(Inference!$B$7&lt;=0,"n/a",IF(Calculator!$B$70&lt;Calculator!$B$53,"Pay per token - saves $"&amp;TEXT(Calculator!$B$53-Calculator!$B$70,"#,##0")&amp;"/month","Self-host - saves $"&amp;TEXT(Calculator!$B$70-Calculator!$B$53,"#,##0")&amp;"/month"))</f>
-        <v>Pay per token - saves $9,322/month</v>
+        <v>Pay per token - saves $4,682/month</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="B42" s="7" t="str">
         <f aca="false">Calculator!$B$128&amp;"  -  "&amp;TEXT(Calculator!$B$31,"#,##0")&amp;" engineer hours/month at $"&amp;TEXT(Calculator!$B$33,"#,##0")&amp;"/hour"</f>
-        <v>Medium  -  60 engineer hours/month at $116/hour</v>
+        <v>Medium  -  20 engineer hours/month at $116/hour</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="B37" s="38" t="n">
         <f aca="false">Calculator!$B$52</f>
-        <v>6960</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="B38" s="40" t="n">
         <f aca="false">Calculator!$B$53</f>
-        <v>12261.7584</v>
+        <v>7621.7584</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="B39" s="41" t="n">
         <f aca="false">Calculator!$B$54</f>
-        <v>147141.1008</v>
+        <v>91461.1008</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="B41" s="42" t="str">
         <f aca="false">IF(Calculator!$B$122=0,"No single machine is big enough for a model this size at this quality setting. Try answering ""Lowest possible cost"" to question 3, or pick a smaller model in question 1.","Running a "&amp;LOWER(LEFT($B$6,FIND(" ",$B$6)-1))&amp;" model this way costs about $"&amp;TEXT(Calculator!$B$53,"#,##0")&amp;" a month, of which $"&amp;TEXT(Calculator!$B$52,"#,##0")&amp;" is the people who look after it and $"&amp;TEXT(Calculator!$B$53-Calculator!$B$52,"#,##0")&amp;" is the cloud bill. That is $"&amp;TEXT(Calculator!$B$54,"#,##0")&amp;" over a year.")</f>
-        <v>Running a large model this way costs about $12,262 a month, of which $6,960 is the people who look after it and $5,302 is the cloud bill. That is $147,141 over a year.</v>
+        <v>Running a large model this way costs about $7,622 a month, of which $2,320 is the people who look after it and $5,302 is the cloud bill. That is $91,461 over a year.</v>
       </c>
       <c r="C41" s="42"/>
     </row>
@@ -4828,7 +4828,7 @@
       </c>
       <c r="B58" s="42" t="str">
         <f aca="false">IF(Inference!$B$7&lt;=0,"Set your expected traffic on the Inference tab to see this comparison.",IF($B$56&lt;$B$38,"Paying per token looks cheaper for this much traffic - about $"&amp;TEXT($B$38-$B$56,"#,##0")&amp;" a month less, and far less to look after. Running your own machines usually only wins once traffic is much heavier, or when the data cannot leave your control.","Running your own machines looks cheaper here - about $"&amp;TEXT($B$56-$B$38,"#,##0")&amp;" a month less - because there is enough traffic to keep them busy."))</f>
-        <v>Paying per token looks cheaper for this much traffic - about $9,822 a month less, and far less to look after. Running your own machines usually only wins once traffic is much heavier, or when the data cannot leave your control.</v>
+        <v>Paying per token looks cheaper for this much traffic - about $5,182 a month less, and far less to look after. Running your own machines usually only wins once traffic is much heavier, or when the data cannot leave your control.</v>
       </c>
       <c r="C58" s="42"/>
     </row>
@@ -5206,7 +5206,7 @@
       </c>
       <c r="B31" s="55" t="n">
         <f aca="false">IF($B$32="",INDEX(Rates!$B$80:$B$82,MATCH($B$128,Rates!$A$80:$A$82,0)),$B$32)</f>
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C31" s="10" t="s">
         <v>146</v>
@@ -5392,11 +5392,11 @@
       </c>
       <c r="B52" s="38" t="n">
         <f aca="false">$B$31*$B$33</f>
-        <v>6960</v>
+        <v>2320</v>
       </c>
       <c r="C52" s="10" t="str">
         <f aca="false">$B$31&amp;" hours x $"&amp;TEXT($B$33,"#,##0")&amp;" per hour ("&amp;$B$128&amp;" support)"</f>
-        <v>60 hours x $116 per hour (Medium support)</v>
+        <v>20 hours x $116 per hour (Medium support)</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="B53" s="46" t="n">
         <f aca="false">SUM(B48:B52)</f>
-        <v>12261.7584</v>
+        <v>7621.7584</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="B54" s="59" t="n">
         <f aca="false">B53*12</f>
-        <v>147141.1008</v>
+        <v>91461.1008</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="B55" s="57" t="n">
         <f aca="false">IFERROR(B53/B45,0)</f>
-        <v>16.7950887573965</v>
+        <v>10.439620863467</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5585,7 +5585,7 @@
       </c>
       <c r="B73" s="38" t="n">
         <f aca="false">$B$53</f>
-        <v>12261.7584</v>
+        <v>7621.7584</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="B74" s="59" t="n">
         <f aca="false">$B$70-$B$53</f>
-        <v>-9321.7584</v>
+        <v>-4681.7584</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="B75" s="42" t="str">
         <f aca="false">IF(Inference!$B$7&lt;=0,"Enter your expected traffic on the Inference tab and this section will fill in.",IF($B$122=0,"Self-hosting has no machine big enough for this model, so paying per token is the only option here at $"&amp;TEXT($B$70,"#,##0")&amp;" per month.",IF($B$70&lt;$B$53,"Paying per token is cheaper by $"&amp;TEXT($B$53-$B$70,"#,##0")&amp;" per month ("&amp;TEXT(1-$B$70/$B$53,"0%")&amp;" less), and there are no machines to keep alive. Raise the requests figure on the Inference tab to find the volume where that reverses.","Self-hosting is cheaper by $"&amp;TEXT($B$70-$B$53,"#,##0")&amp;" per month ("&amp;TEXT(1-$B$53/$B$70,"0%")&amp;" less), because you are running enough volume to fill the machines you rent.")))</f>
-        <v>Paying per token is cheaper by $9,322 per month (76% less), and there are no machines to keep alive. Raise the requests figure on the Inference tab to find the volume where that reverses.</v>
+        <v>Paying per token is cheaper by $4,682 per month (61% less), and there are no machines to keep alive. Raise the requests figure on the Inference tab to find the volume where that reverses.</v>
       </c>
       <c r="C75" s="42"/>
       <c r="D75" s="42"/>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="B29" s="38" t="n">
         <f aca="false">Calculator!$B$53</f>
-        <v>12261.7584</v>
+        <v>7621.7584</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="B31" s="75" t="n">
         <f aca="false">IFERROR($B$29/$B$30,0)</f>
-        <v>61.308792</v>
+        <v>38.108792</v>
       </c>
       <c r="C31" s="10" t="s">
         <v>246</v>
@@ -6066,7 +6066,7 @@
       </c>
       <c r="B32" s="58" t="n">
         <f aca="false">IFERROR($B$29/$B$7*1000,0)</f>
-        <v>24.5235168</v>
+        <v>15.2435168</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="B33" s="76" t="n">
         <f aca="false">IFERROR($B$29/$B$7,0)</f>
-        <v>0.0245235168</v>
+        <v>0.0152435168</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6411,11 +6411,11 @@
       </c>
       <c r="B21" s="84" t="n">
         <f aca="false">Calculator!$B$52</f>
-        <v>6960</v>
+        <v>2320</v>
       </c>
       <c r="C21" s="84" t="n">
         <f aca="false">Calculator!$B$52</f>
-        <v>6960</v>
+        <v>2320</v>
       </c>
       <c r="D21" s="10" t="s">
         <v>270</v>
@@ -6427,11 +6427,11 @@
       </c>
       <c r="B22" s="85" t="n">
         <f aca="false">SUM(B17:B21)</f>
-        <v>13083.169264</v>
+        <v>8443.169264</v>
       </c>
       <c r="C22" s="85" t="n">
         <f aca="false">SUM(C17:C21)</f>
-        <v>12261.7584</v>
+        <v>7621.7584</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6440,11 +6440,11 @@
       </c>
       <c r="B23" s="85" t="n">
         <f aca="false">B22*12</f>
-        <v>156998.031168</v>
+        <v>101318.031168</v>
       </c>
       <c r="C23" s="85" t="n">
         <f aca="false">C22*12</f>
-        <v>147141.1008</v>
+        <v>91461.1008</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="B25" s="86" t="str">
         <f aca="false">IF(AND($B$62=0,$B$63=0),"Neither cloud has a single machine with enough GPU memory. Use INT4, a smaller model, or plan on splitting the model across several machines.",IF($B$62=0,"Only Microsoft Azure has a machine big enough for this model.",IF($B$63=0,"Only Google Cloud has a machine big enough for this model.",IF(B22&lt;C22,"Google Cloud saves about $"&amp;TEXT(C22-B22,"#,##0")&amp;" per month ("&amp;TEXT(1-B22/C22,"0.0%")&amp;" less)",IF(C22&lt;B22,"Microsoft Azure saves about $"&amp;TEXT(B22-C22,"#,##0")&amp;" per month ("&amp;TEXT(1-C22/B22,"0.0%")&amp;" less)","The two are within a dollar of each other")))))</f>
-        <v>Microsoft Azure saves about $821 per month (6.3% less)</v>
+        <v>Microsoft Azure saves about $821 per month (9.7% less)</v>
       </c>
       <c r="C25" s="86"/>
       <c r="D25" s="86"/>
@@ -6547,11 +6547,11 @@
       </c>
       <c r="B36" s="88" t="n">
         <f aca="false">B22</f>
-        <v>13083.169264</v>
+        <v>8443.169264</v>
       </c>
       <c r="C36" s="88" t="n">
         <f aca="false">C22</f>
-        <v>12261.7584</v>
+        <v>7621.7584</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="B39" s="86" t="str">
         <f aca="false">IF(Inference!$B$7&lt;=0,"Enter your expected traffic on the Inference tab to compare against pay-per-token pricing.","Cheapest overall: "&amp;IF(MIN($B$22,$C$22,$B$35,$C$35)=$B$35,"pay per token on Google Cloud using "&amp;$B$32,IF(MIN($B$22,$C$22,$B$35,$C$35)=$C$35,"pay per token on Azure using "&amp;$C$32,IF(MIN($B$22,$C$22,$B$35,$C$35)=$B$22,"self-hosting on Google Cloud on "&amp;$B$5,"self-hosting on Azure on "&amp;$C$5)))&amp;"  at about $"&amp;TEXT(MIN($B$22,$C$22,$B$35,$C$35),"#,##0")&amp;" per month, versus $"&amp;TEXT(MAX($B$22,$C$22,$B$35,$C$35),"#,##0")&amp;" for the most expensive of the four.")</f>
-        <v>Cheapest overall: pay per token on Google Cloud using Gemini 2.5 Flash-Lite  at about $2,440 per month, versus $13,083 for the most expensive of the four.</v>
+        <v>Cheapest overall: pay per token on Google Cloud using Gemini 2.5 Flash-Lite  at about $2,440 per month, versus $8,443 for the most expensive of the four.</v>
       </c>
       <c r="C39" s="86"/>
       <c r="D39" s="86"/>
@@ -11199,7 +11199,7 @@
         <v>512</v>
       </c>
       <c r="B80" s="111" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C80" s="109" t="s">
         <v>550</v>
@@ -11213,7 +11213,7 @@
         <v>516</v>
       </c>
       <c r="B81" s="111" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C81" s="109" t="s">
         <v>552</v>
@@ -11227,7 +11227,7 @@
         <v>518</v>
       </c>
       <c r="B82" s="111" t="n">
-        <v>160</v>
+        <v>30</v>
       </c>
       <c r="C82" s="109" t="s">
         <v>554</v>
